--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_CDP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_CDP.xlsx
@@ -422,23 +422,342 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>height_cm</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>bpg</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>CDP_B._WHITAKER</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B. Whitaker</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CDP_B._GOMES</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B. Gomes</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>24.2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CDP_M._LAMUT</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>M. Lamut</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>24.2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CDP_A._BAH</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A. Bah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CDP_J._RODRIGUES</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>J. Rodrigues</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>21.5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -453,24 +772,82 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>players</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pf_per40</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pa_per40</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>net_per40</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>A. Bah | B. Whitaker</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>16.5</v>
       </c>
     </row>
   </sheetData>
@@ -484,12 +861,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -546,32 +923,100 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>shooting</t>
+          <t>rotation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>most_used_zone</t>
+          <t>most_used_player</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>scoring</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>primary_scorer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A. Bah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>lineups</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>base_lineup</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut (21.5 min)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>lineups</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>best_lineup</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut (18.6 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>shooting</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>most_used_zone</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>shooting</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>best_zone</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
@@ -632,16 +1077,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77.5</v>
+        <v>75.8</v>
       </c>
       <c r="C2" t="n">
-        <v>76.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="3">
@@ -651,16 +1096,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>109.5</v>
+        <v>105</v>
       </c>
       <c r="C3" t="n">
-        <v>110.4</v>
+        <v>106.2</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.9</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="4">
@@ -670,16 +1115,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>81.8</v>
+        <v>86.5</v>
       </c>
       <c r="C4" t="n">
-        <v>110.4</v>
+        <v>106.6</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-28.6</v>
+        <v>-20.2</v>
       </c>
     </row>
     <row r="5">
@@ -689,16 +1134,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.7</v>
+        <v>18.5</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>27.7</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="6">
@@ -711,13 +1156,13 @@
         <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.2</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="7">
@@ -733,7 +1178,7 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -749,13 +1194,13 @@
         <v>0.4</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -765,16 +1210,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10">
@@ -790,7 +1235,7 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>-0.1</v>
@@ -853,7 +1298,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>League-average pace; rhythm control matters more than pure speed against them.</t>
+          <t>Below-average pace; they are more comfortable when the game stays organized in the half court.</t>
         </is>
       </c>
     </row>
@@ -901,7 +1346,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Above-average foul volume; contact pressure and discipline both matter in this matchup.</t>
+          <t>Foul profile sits near league average; physicality is part of the game, but not their defining trait.</t>
         </is>
       </c>
     </row>
@@ -928,7 +1373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -955,7 +1400,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Own the rhythm: pace itself is not the main separator, so the quality of possessions matters more than speed.</t>
+          <t>Control the rhythm: they are more comfortable in a controlled half-court game, so do not let them play cleanly into structure.</t>
         </is>
       </c>
     </row>
@@ -980,6 +1425,18 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>Do not overreact to the arc: make them finish over traffic instead of giving up easy paint comfort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Game Plan Keys</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Know the first reference: A. Bah is a bench spacer, and the plan should start with taking away his comfort.</t>
         </is>
       </c>
     </row>
@@ -994,7 +1451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1016,48 +1473,96 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Perimeter Shooting</t>
+          <t>Offense</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from B. Whitaker and J. Costa; contest, but do not over-help into secondary advantages.</t>
+          <t>The main offensive references are B. Whitaker and B. Gomes; load the scouting plan into those names first.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Scoring Areas</t>
+          <t>Perimeter Shooting</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Their offense naturally flows toward Paint Non-RA; protect that area early in possessions.</t>
+          <t>Priority closeouts start with B. Gomes and A. Bah; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Scoring Areas</t>
+          <t>Perimeter Shooting</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially J. Okemirie, M. Lamut, and A. Bah; force them away from preferred areas.</t>
+          <t>Some perimeter volume comes from B. Whitaker and J. Costa; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Scoring Areas</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Their offense naturally flows toward Restricted Area; protect that area early in possessions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Scoring Areas</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Several players have clear comfort zones, especially A. Bah, J. Okemirie, and M. Lamut; force them away from preferred areas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Recognize the main duo/trio combinations: A. Bah | B. Whitaker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Defensive Emphasis</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Second-chance threat; the first stop is not enough against this team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Defensive Emphasis</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Do not lose B. Gomes and A. Bah in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1072,23 +1577,238 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>main_zone</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>role_note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>CDP_B._WHITAKER</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B. Whitaker</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>paint finisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CDP_B._GOMES</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B. Gomes</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CDP_M._LAMUT</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>M. Lamut</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>inside scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CDP_A._BAH</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A. Bah</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>bench spacer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CDP_J._RODRIGUES</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>J. Rodrigues</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>inside scorer</t>
         </is>
       </c>
     </row>
@@ -1103,18 +1823,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -1197,41 +1917,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CDP_B._WHITAKER</t>
+          <t>CDP_B._GOMES</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B. Whitaker</t>
+          <t>B. Gomes</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -1243,41 +1963,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CDP_J._COSTA</t>
+          <t>CDP_A._BAH</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>J. Costa</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -1289,110 +2009,140 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>22</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>40.9%</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>30.1%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CDP_B._WHITAKER</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B. Whitaker</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CDP_J._COSTA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>J. Costa</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>20</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>65.0%</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>27.4%</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>12</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>16.4%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CDP_J._RODRIGUES</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>J. Rodrigues</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1410,23 +2160,23 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>27.6%</t>
         </is>
       </c>
     </row>
@@ -1446,42 +2196,34 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>26.1%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CDP_J._OKEMIRIE</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>J. Okemirie</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
@@ -1490,42 +2232,34 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>22.4%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CDP_M._LAMUT</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>M. Lamut</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -1534,42 +2268,34 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CDP_A._BAH</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>A. Bah</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -1578,23 +2304,23 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>6.0%</t>
         </is>
       </c>
     </row>
@@ -1606,12 +2332,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_A._BAH</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1626,19 +2352,239 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="M12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>42.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CDP_J._OKEMIRIE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>J. Okemirie</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
         <v>1.2</v>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>41.7%</t>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CDP_M._LAMUT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>M. Lamut</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>7</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CDP_B._GOMES</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B. Gomes</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CDP_D._BUCCILLI</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>D. Buccilli</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CDP_B._WHITAKER</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B. Whitaker</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>30.0%</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_CDP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_CDP.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -515,192 +515,192 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_M._LAMUT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>M. Lamut</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CDP_M._LAMUT</t>
+          <t>CDP_A._BAH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDP_A._BAH</t>
+          <t>CDP_J._RODRIGUES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>J. Rodrigues</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -712,50 +712,258 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CDP_J._RODRIGUES</t>
+          <t>CDP_D._BUCCILLI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Rodrigues</t>
+          <t>D. Buccilli</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CDP_J._OKEMIRIE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>J. Okemirie</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CDP_B._GOMES</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>B. Gomes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
         <v>2</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>21.5</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>24.2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CDP_M._RODRIGUES</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M. Rodrigues</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CDP_J._COSTA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>J. Costa</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -772,12 +980,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -838,16 +1046,103 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>46.2</v>
+        <v>63.2</v>
       </c>
       <c r="E2" t="n">
-        <v>71.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="F2" t="n">
-        <v>55.4</v>
+        <v>57.6</v>
       </c>
       <c r="G2" t="n">
-        <v>16.5</v>
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>trio</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A. Bah | B. Whitaker | M. Lamut</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Best defense</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>J. Rodrigues | M. Lamut</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Best net</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>J. Rodrigues | M. Lamut</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>21.3</v>
       </c>
     </row>
   </sheetData>
@@ -967,7 +1262,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut (21.5 min)</t>
+          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut</t>
         </is>
       </c>
     </row>
@@ -984,7 +1279,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut (18.6 net)</t>
+          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut</t>
         </is>
       </c>
     </row>
@@ -1077,16 +1372,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75.8</v>
+        <v>74.5</v>
       </c>
       <c r="C2" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.8</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="3">
@@ -1096,16 +1391,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C3" t="n">
-        <v>106.2</v>
+        <v>105.6</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.2</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="4">
@@ -1115,16 +1410,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>86.5</v>
+        <v>93.5</v>
       </c>
       <c r="C4" t="n">
-        <v>106.6</v>
+        <v>105.9</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-20.2</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -1134,16 +1429,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.5</v>
+        <v>8.6</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>18.9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="6">
@@ -1153,16 +1448,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>12.3</v>
       </c>
       <c r="C6" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.8</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="7">
@@ -1178,10 +1473,10 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -1191,16 +1486,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C8" t="n">
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -1210,16 +1505,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>19.7</v>
       </c>
       <c r="C9" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10">
@@ -1229,16 +1524,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C10" t="n">
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -1248,16 +1543,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C11" t="n">
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1</v>
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
@@ -1322,7 +1617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Second-chance threat; the first stop is not enough against this team.</t>
+          <t>Offensive rebounding is around league average; box-outs matter but this is not their main edge.</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1629,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Loose enough with the ball to be pressured; there are possessions to steal here.</t>
+          <t>Better-than-average ball security; they do not hand away many live possessions.</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1641,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Foul profile sits near league average; physicality is part of the game, but not their defining trait.</t>
+          <t>Lower foul volume than league average; this is not a team that wants constant contact chaos.</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Finish possessions: the first stop is not enough against this team because the offensive glass is a real source of extra points.</t>
+          <t>Do not overreact to the arc: make them finish over traffic instead of giving up easy paint comfort.</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1719,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Do not overreact to the arc: make them finish over traffic instead of giving up easy paint comfort.</t>
+          <t>Know the first reference: A. Bah is a bench spacer, and the plan should start with taking away his comfort.</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1731,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Know the first reference: A. Bah is a bench spacer, and the plan should start with taking away his comfort.</t>
+          <t>Closeout discipline matters: M. Rodrigues, B. Gomes are the first perimeter names you cannot lose in help situations.</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1478,7 +1773,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The main offensive references are B. Whitaker and B. Gomes; load the scouting plan into those names first.</t>
+          <t>The main offensive references are B. Whitaker and M. Lamut; load the scouting plan into those names first.</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1785,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priority closeouts start with B. Gomes and A. Bah; do not lose them in help-and-recover situations.</t>
+          <t>Priority closeouts start with M. Rodrigues, B. Gomes, and A. Bah; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1797,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from B. Whitaker and J. Costa; contest, but do not over-help into secondary advantages.</t>
+          <t>Some perimeter volume comes from A. Bah and B. Whitaker; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1821,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially A. Bah, J. Okemirie, and M. Lamut; force them away from preferred areas.</t>
+          <t>Several players have clear comfort zones, especially A. Bah, B. Whitaker, and J. Okemirie; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
@@ -1538,31 +1833,55 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Recognize the main duo/trio combinations: A. Bah | B. Whitaker.</t>
+          <t>Most-used lineup to rehearse first: A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Defensive Emphasis</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Second-chance threat; the first stop is not enough against this team.</t>
+          <t>Secondary lineup to recognize: A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Recognize the main duo/trio combinations: A. Bah | B. Whitaker and A. Bah | B. Whitaker | M. Lamut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Defensive Emphasis</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Do not lose B. Gomes and A. Bah in help-and-recover situations.</t>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Offensive rebounding is around league average; box-outs matter but this is not their main edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Defensive Emphasis</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Do not lose M. Rodrigues and B. Gomes in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1644,157 +1963,157 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25.6</v>
+        <v>26.8</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>12.7</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>paint finisher</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_M._LAMUT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>M. Lamut</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="D3" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>paint finisher</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CDP_M._LAMUT</t>
+          <t>CDP_A._BAH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24.2</v>
+        <v>23.4</v>
       </c>
       <c r="D4" t="n">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>inside scorer</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDP_A._BAH</t>
+          <t>CDP_J._RODRIGUES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>J. Rodrigues</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.2</v>
+        <v>22.4</v>
       </c>
       <c r="D5" t="n">
-        <v>13.5</v>
+        <v>2.3</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>bench spacer</t>
+          <t>inside scorer</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CDP_J._RODRIGUES</t>
+          <t>CDP_D._BUCCILLI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Rodrigues</t>
+          <t>D. Buccilli</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.5</v>
+        <v>17.6</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1803,12 +2122,44 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>inside scorer</t>
+          <t>paint finisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CDP_J._OKEMIRIE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>J. Okemirie</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>paint finisher</t>
         </is>
       </c>
     </row>
@@ -1823,7 +2174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1922,32 +2273,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_M._RODRIGUES</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>M. Rodrigues</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1968,29 +2319,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CDP_A._BAH</t>
+          <t>CDP_B._GOMES</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>B. Gomes</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -2009,41 +2360,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CDP_B._WHITAKER</t>
+          <t>CDP_A._BAH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B. Whitaker</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -2055,25 +2406,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CDP_J._COSTA</t>
+          <t>CDP_B._WHITAKER</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>J. Costa</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2082,14 +2433,14 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -2106,36 +2457,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CDP_J._RODRIGUES</t>
+          <t>CDP_A._BAH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>J. Rodrigues</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -2147,110 +2498,140 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>37</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>75.7%</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>27.6%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CDP_B._WHITAKER</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B. Whitaker</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>14</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>35</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>35</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>37.1%</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>26.1%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CDP_J._GOMES</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>J. Gomes</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>30</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>22.4%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CDP_J._COSTA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>J. Costa</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>13</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2268,23 +2649,23 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>29.5%</t>
         </is>
       </c>
     </row>
@@ -2304,42 +2685,34 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>28.0%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>CDP_A._BAH</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>A. Bah</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -2348,42 +2721,34 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>23.5%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>CDP_J._OKEMIRIE</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>J. Okemirie</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -2392,42 +2757,34 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CDP_M._LAMUT</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>M. Lamut</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -2436,23 +2793,23 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>5.5%</t>
         </is>
       </c>
     </row>
@@ -2464,12 +2821,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_A._BAH</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2484,19 +2841,19 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>41.0%</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2865,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CDP_D._BUCCILLI</t>
+          <t>CDP_B._WHITAKER</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>D. Buccilli</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -2524,23 +2881,23 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>34.3%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2909,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CDP_B._WHITAKER</t>
+          <t>CDP_J._OKEMIRIE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B. Whitaker</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2572,19 +2929,239 @@
         </is>
       </c>
       <c r="K17" t="n">
+        <v>10</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CDP_M._LAMUT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>M. Lamut</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CDP_M._RODRIGUES</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>M. Rodrigues</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>9</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>52.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CDP_D._BUCCILLI</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>D. Buccilli</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>7</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CDP_B._GOMES</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B. Gomes</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>7</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CDP_J._COSTA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>J. Costa</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
         <v>6</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>30.0%</t>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -2599,24 +3176,95 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>lineup_players</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pf_per40</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pa_per40</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>net_per40</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>Base lineup</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Best defense</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>27.3</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_CDP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_CDP.xlsx
@@ -422,11 +422,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -515,41 +515,41 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -567,41 +567,41 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -619,36 +619,36 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -671,36 +671,36 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -723,36 +723,36 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -764,84 +764,88 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDP_J._OKEMIRIE</t>
+          <t>CDP_B._GOMES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Okemirie</t>
+          <t>Betinho Gomes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="E7" t="n">
         <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>1.0</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_J._OKEMIRIE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -851,7 +855,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -861,7 +865,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -879,26 +883,26 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -908,7 +912,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -920,50 +924,102 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CDP_J._COSTA</t>
+          <t>CDP_J._PEDRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Costa</t>
+          <t>J. Pedro</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CDP_J._COSTA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J. Costa</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -984,8 +1040,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -1042,84 +1098,84 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A. Bah | B. Whitaker</t>
+          <t>A. Bah | M. Lamut</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>63.2</v>
+        <v>82.3</v>
       </c>
       <c r="E2" t="n">
-        <v>67.7</v>
+        <v>73.8</v>
       </c>
       <c r="F2" t="n">
-        <v>57.6</v>
+        <v>63.6</v>
       </c>
       <c r="G2" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>trio</t>
+          <t>duo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Most used</t>
+          <t>Best net</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A. Bah | B. Whitaker | M. Lamut</t>
+          <t>J. Rodrigues | M. Lamut</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>54.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>70.8</v>
+        <v>77</v>
       </c>
       <c r="F3" t="n">
-        <v>56.8</v>
+        <v>60.6</v>
       </c>
       <c r="G3" t="n">
-        <v>14</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>duo</t>
+          <t>trio</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Best defense</t>
+          <t>Most used</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>J. Rodrigues | M. Lamut</t>
+          <t>A. Bah | B. Whitaker | M. Lamut</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>48.8</v>
+        <v>70</v>
       </c>
       <c r="E4" t="n">
-        <v>77.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>56.6</v>
+        <v>61.1</v>
       </c>
       <c r="G4" t="n">
-        <v>21.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>duo</t>
+          <t>trio</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1129,20 +1185,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>J. Rodrigues | M. Lamut</t>
+          <t>A. Bah | J. Rodrigues | M. Lamut</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>48.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>77.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>56.6</v>
+        <v>60.3</v>
       </c>
       <c r="G5" t="n">
-        <v>21.3</v>
+        <v>16.6</v>
       </c>
     </row>
   </sheetData>
@@ -1245,7 +1301,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1352,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
     </row>
@@ -1372,16 +1428,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>74.5</v>
+        <v>75.7</v>
       </c>
       <c r="C2" t="n">
-        <v>78.8</v>
+        <v>79.3</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.2</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="3">
@@ -1391,16 +1447,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>98.3</v>
       </c>
       <c r="C3" t="n">
-        <v>105.6</v>
+        <v>103.9</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.6</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="4">
@@ -1410,16 +1466,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>93.5</v>
+        <v>95.8</v>
       </c>
       <c r="C4" t="n">
-        <v>105.9</v>
+        <v>104</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>-12.5</v>
+        <v>-8.199999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1429,16 +1485,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.6</v>
+        <v>2.5</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>8.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="6">
@@ -1448,16 +1504,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="C6" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>-5</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="7">
@@ -1473,7 +1529,7 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
         <v>-0</v>
@@ -1492,10 +1548,10 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1505,7 +1561,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.7</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
         <v>20.7</v>
@@ -1514,7 +1570,7 @@
         <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>-1</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="10">
@@ -1530,7 +1586,7 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>-0</v>
@@ -1549,7 +1605,7 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>-0</v>
@@ -1629,7 +1685,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Better-than-average ball security; they do not hand away many live possessions.</t>
+          <t>Turnover profile is close to league average; pressure helps, but it is not the whole plan.</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1697,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lower foul volume than league average; this is not a team that wants constant contact chaos.</t>
+          <t>Foul profile sits near league average; physicality is part of the game, but not their defining trait.</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1709,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Less three-point dependent than league average; more of their offense is built away from pure perimeter volume.</t>
+          <t>Perimeter volume is close to league average; shot mix alone does not define them.</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1707,7 +1763,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Do not overreact to the arc: make them finish over traffic instead of giving up easy paint comfort.</t>
+          <t>Know the first reference: B. Whitaker is a bench spacer, and the plan should start with taking away his comfort.</t>
         </is>
       </c>
     </row>
@@ -1719,19 +1775,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Know the first reference: A. Bah is a bench spacer, and the plan should start with taking away his comfort.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Game Plan Keys</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Closeout discipline matters: M. Rodrigues, B. Gomes are the first perimeter names you cannot lose in help situations.</t>
+          <t>Closeout discipline matters: M. Rodrigues, Betinho Gomes are the first perimeter names you cannot lose in help situations.</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1829,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priority closeouts start with M. Rodrigues, B. Gomes, and A. Bah; do not lose them in help-and-recover situations.</t>
+          <t>Priority closeouts start with M. Rodrigues, Betinho Gomes, and B. Whitaker; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1853,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Their offense naturally flows toward Restricted Area; protect that area early in possessions.</t>
+          <t>Their offense naturally flows toward Above the Break 3; protect that area early in possessions.</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1865,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially A. Bah, B. Whitaker, and J. Okemirie; force them away from preferred areas.</t>
+          <t>Several players have clear comfort zones, especially A. Bah, B. Whitaker, and M. Lamut; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1901,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Recognize the main duo/trio combinations: A. Bah | B. Whitaker and A. Bah | B. Whitaker | M. Lamut.</t>
+          <t>Recognize the main duo/trio combinations: A. Bah | M. Lamut and J. Rodrigues | M. Lamut.</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1925,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Do not lose M. Rodrigues and B. Gomes in help-and-recover situations.</t>
+          <t>Do not lose M. Rodrigues and Betinho Gomes in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1899,14 +1943,14 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1963,17 +2007,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26.8</v>
+        <v>27.4</v>
       </c>
       <c r="D2" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1999,13 +2043,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24.4</v>
+        <v>25.4</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2019,7 +2063,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>paint finisher</t>
+          <t>primary handler</t>
         </is>
       </c>
     </row>
@@ -2035,17 +2079,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23.4</v>
+        <v>24.1</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>11.8</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2071,13 +2115,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2107,17 +2151,17 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2134,32 +2178,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDP_J._OKEMIRIE</t>
+          <t>CDP_BETINHO_GOMES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Okemirie</t>
+          <t>Betinho Gomes</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.3</v>
+        <v>22.8</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>10.7</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>paint finisher</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
@@ -2178,8 +2226,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -2282,20 +2330,20 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -2319,32 +2367,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_BETINHO_GOMES</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>Betinho Gomes</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2365,12 +2413,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CDP_A._BAH</t>
+          <t>CDP_B._WHITAKER</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A. Bah</t>
+          <t>B. Whitaker</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -2383,14 +2431,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2411,29 +2459,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CDP_B._WHITAKER</t>
+          <t>CDP_A._BAH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B. Whitaker</t>
+          <t>A. Bah</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H5" t="n">
         <v>0.9</v>
@@ -2466,20 +2514,20 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H6" t="n">
         <v>0.9</v>
@@ -2512,23 +2560,23 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2549,16 +2597,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CDP_J._GOMES</t>
+          <t>CDP_J._COSTA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>J. Gomes</t>
+          <t>J. Costa</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2567,14 +2615,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2595,12 +2643,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CDP_J._COSTA</t>
+          <t>CDP_J._GOMES</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>J. Costa</t>
+          <t>J. Gomes</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -2613,14 +2661,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -2649,23 +2697,23 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>29.3%</t>
         </is>
       </c>
     </row>
@@ -2685,23 +2733,23 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.4%</t>
         </is>
       </c>
     </row>
@@ -2725,19 +2773,19 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>22.6%</t>
         </is>
       </c>
     </row>
@@ -2761,19 +2809,19 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>11.3%</t>
         </is>
       </c>
     </row>
@@ -2797,19 +2845,19 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>4.9%</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2889,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -2853,7 +2901,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -2885,19 +2933,19 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
     </row>
@@ -2909,12 +2957,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CDP_J._OKEMIRIE</t>
+          <t>CDP_M._LAMUT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>J. Okemirie</t>
+          <t>M. Lamut</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2929,7 +2977,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -2941,7 +2989,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>48.4%</t>
         </is>
       </c>
     </row>
@@ -2953,12 +3001,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CDP_M._LAMUT</t>
+          <t>CDP_J._OKEMIRIE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2973,19 +3021,19 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -3017,19 +3065,19 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3089,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CDP_D._BUCCILLI</t>
+          <t>CDP_BETINHO_GOMES</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>D. Buccilli</t>
+          <t>Betinho Gomes</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -3057,23 +3105,23 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
     </row>
@@ -3085,12 +3133,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CDP_B._GOMES</t>
+          <t>CDP_D._BUCCILLI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>D. Buccilli</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -3101,23 +3149,23 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -3129,12 +3177,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CDP_J._COSTA</t>
+          <t>CDP_J._RODRIGUES</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>J. Costa</t>
+          <t>J. Rodrigues</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -3145,23 +3193,23 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>36.8%</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3279,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26.4</v>
+        <v>36.2</v>
       </c>
       <c r="D2" t="n">
-        <v>75.7</v>
+        <v>68.5</v>
       </c>
       <c r="E2" t="n">
-        <v>48.5</v>
+        <v>58.5</v>
       </c>
       <c r="F2" t="n">
-        <v>27.3</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="3">
@@ -3255,16 +3303,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.4</v>
+        <v>36.2</v>
       </c>
       <c r="D3" t="n">
-        <v>75.7</v>
+        <v>68.5</v>
       </c>
       <c r="E3" t="n">
-        <v>48.5</v>
+        <v>58.5</v>
       </c>
       <c r="F3" t="n">
-        <v>27.3</v>
+        <v>9.9</v>
       </c>
     </row>
   </sheetData>
